--- a/data/manual/eu_wob_prices.xlsx
+++ b/data/manual/eu_wob_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E44268-A565-4B13-BA52-CA54D75B8A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CE384E2-2203-4D1C-A093-5CBF013FD204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
@@ -670,7 +670,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -696,13 +696,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>1837</v>
+        <v>1865</v>
       </c>
       <c r="C3" s="3">
-        <v>2138</v>
+        <v>2162</v>
       </c>
       <c r="D3" s="3">
-        <v>1799.99</v>
+        <v>1820.57</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -713,20 +713,20 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1958.53</v>
+        <v>1977.27</v>
       </c>
       <c r="C4" s="3">
-        <v>2348.7800000000002</v>
+        <v>2335.08</v>
       </c>
       <c r="D4" s="3">
-        <v>1533.4</v>
+        <v>1597</v>
       </c>
       <c r="E4" s="3">
-        <v>578.49</v>
+        <v>598.84</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>982</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -734,16 +734,16 @@
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1662.8</v>
+        <v>1649.1</v>
       </c>
       <c r="C5" s="3">
-        <v>1892.9</v>
+        <v>1873.8</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>632.9</v>
+        <v>598</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -751,20 +751,20 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1826.5</v>
+        <v>1803.33</v>
       </c>
       <c r="C6" s="3">
-        <v>1983.88</v>
+        <v>1953.75</v>
       </c>
       <c r="D6" s="3">
-        <v>1670</v>
+        <v>1620</v>
       </c>
       <c r="E6" s="3">
         <v>940.8</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>892</v>
+        <v>907</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -772,13 +772,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1743.73</v>
+        <v>1759.61</v>
       </c>
       <c r="C7" s="3">
-        <v>2029.91</v>
+        <v>2020.75</v>
       </c>
       <c r="D7" s="3">
-        <v>1671.1</v>
+        <v>1678.38</v>
       </c>
       <c r="E7" s="3">
         <v>1059.51</v>
@@ -791,18 +791,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1846.704285246974</v>
+        <v>1859.0873682915831</v>
       </c>
       <c r="C8" s="3">
-        <v>1952.1180896303565</v>
+        <v>1921.2004427862737</v>
       </c>
       <c r="D8" s="3">
-        <v>1495.0932286555446</v>
+        <v>1534.8284203189701</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>889.51586522734704</v>
+        <v>927.39125087122306</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -810,13 +810,13 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2604.8565121412807</v>
+        <v>2658.2651040830524</v>
       </c>
       <c r="C9" s="3">
-        <v>2488.4607666064621</v>
+        <v>2501.7391769679457</v>
       </c>
       <c r="D9" s="3">
-        <v>2449.5283965482645</v>
+        <v>2462.8083694547008</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -827,18 +827,18 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>1945</v>
+        <v>1920</v>
       </c>
       <c r="C10" s="3">
-        <v>2096</v>
+        <v>2013</v>
       </c>
       <c r="D10" s="3">
-        <v>1715</v>
+        <v>1706</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -846,13 +846,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>2370.0952380952381</v>
+        <v>2318.8260869565224</v>
       </c>
       <c r="C11" s="3">
-        <v>2552.9130434782605</v>
+        <v>2536.0454545454545</v>
       </c>
       <c r="D11" s="3">
-        <v>2048.2340277777776</v>
+        <v>2072.4888888888891</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -863,18 +863,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>2211.71</v>
+        <v>2212.2199999999998</v>
       </c>
       <c r="C12" s="3">
-        <v>2355.48</v>
+        <v>2328.25</v>
       </c>
       <c r="D12" s="3">
-        <v>1907.08</v>
+        <v>1892.57</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>1013.94</v>
+        <v>1028.8599999999999</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -882,18 +882,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>2196</v>
+        <v>2214</v>
       </c>
       <c r="C13" s="3">
-        <v>2254</v>
+        <v>2270</v>
       </c>
       <c r="D13" s="3">
-        <v>1726.4</v>
+        <v>1698.1</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>1049</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -901,10 +901,10 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>2203</v>
+        <v>2199</v>
       </c>
       <c r="C14" s="3">
-        <v>2166</v>
+        <v>2118</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3">
@@ -918,20 +918,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1725.568103447765</v>
+        <v>1754.0858764191948</v>
       </c>
       <c r="C15" s="3">
-        <v>1928.0696660354984</v>
+        <v>1941.8789433776333</v>
       </c>
       <c r="D15" s="3">
-        <v>1928.0696660354984</v>
+        <v>1941.8789433776333</v>
       </c>
       <c r="E15" s="3">
-        <v>1295.1332245785752</v>
+        <v>1304.603839728316</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>983.92022651677871</v>
+        <v>1014.847193641408</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -956,20 +956,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>2072.6999999999998</v>
+        <v>2021.02</v>
       </c>
       <c r="C17" s="3">
-        <v>2273.46</v>
+        <v>2240.73</v>
       </c>
       <c r="D17" s="3">
-        <v>2063.1</v>
+        <v>2053</v>
       </c>
       <c r="E17" s="3">
-        <v>713.73</v>
+        <v>747.09</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>770.59</v>
+        <v>781.09</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -977,18 +977,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1962.4</v>
+        <v>1942.8</v>
       </c>
       <c r="C18" s="3">
-        <v>2120.33</v>
+        <v>2072.17</v>
       </c>
       <c r="D18" s="3">
-        <v>1884.38</v>
+        <v>1836.21</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>948.25</v>
+        <v>985.6</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -996,18 +996,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1937.98</v>
+        <v>1924.94</v>
       </c>
       <c r="C19" s="3">
-        <v>2240.7399999999998</v>
+        <v>2205.09</v>
       </c>
       <c r="D19" s="3">
-        <v>1574.9</v>
+        <v>1577.25</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>821.68</v>
+        <v>856.18</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1015,18 +1015,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1837</v>
+        <v>1876</v>
       </c>
       <c r="C20" s="3">
-        <v>2057</v>
+        <v>2045</v>
       </c>
       <c r="D20" s="3">
-        <v>1539</v>
+        <v>1536</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>830</v>
+        <v>919</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1051,16 +1051,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>2431.83</v>
+        <v>2461.96</v>
       </c>
       <c r="C22" s="3">
-        <v>2506.06</v>
+        <v>2481.86</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>954.74</v>
+        <v>960.92</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1068,22 +1068,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1519.5932977673426</v>
+        <v>1570.2289837417384</v>
       </c>
       <c r="C23" s="3">
-        <v>1764.4552738558384</v>
+        <v>1794.6871203469439</v>
       </c>
       <c r="D23" s="3">
-        <v>1662.7723701014072</v>
+        <v>1691.4694954589233</v>
       </c>
       <c r="E23" s="3">
-        <v>855.97651885483185</v>
+        <v>753.42972262350975</v>
       </c>
       <c r="F23" s="3">
-        <v>630.43169534332628</v>
+        <v>655.41248342928134</v>
       </c>
       <c r="G23" s="3">
-        <v>740.05683525740915</v>
+        <v>773.37468583966722</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1091,20 +1091,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>2081</v>
+        <v>2110</v>
       </c>
       <c r="C24" s="3">
-        <v>2155</v>
+        <v>2148</v>
       </c>
       <c r="D24" s="3">
-        <v>2204</v>
+        <v>2183</v>
       </c>
       <c r="E24" s="3">
-        <v>1106.68</v>
+        <v>1101.1300000000001</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>922</v>
+        <v>934</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1112,20 +1112,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>1886.3500927609018</v>
+        <v>1897.6203859846357</v>
       </c>
       <c r="C25" s="3">
-        <v>2049.5867923467572</v>
+        <v>2041.3022297170698</v>
       </c>
       <c r="D25" s="3">
-        <v>1589.2041302025748</v>
+        <v>1580.4684279557803</v>
       </c>
       <c r="E25" s="3">
-        <v>1044.3903078912356</v>
+        <v>1015.7729061270378</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>1088.7637501639715</v>
+        <v>883.63687464867917</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1133,16 +1133,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="C26" s="3">
-        <v>1972</v>
+        <v>1919</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>818</v>
+        <v>866</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1150,18 +1150,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1763.09</v>
+        <v>1761.48</v>
       </c>
       <c r="C27" s="3">
-        <v>1981.49</v>
+        <v>1918.27</v>
       </c>
       <c r="D27" s="3">
-        <v>1628.87</v>
+        <v>1569.8</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>983.72</v>
+        <v>981.72</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1169,20 +1169,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1849.0983979999999</v>
+        <v>1789.5447049999998</v>
       </c>
       <c r="C28" s="3">
-        <v>1917.638549</v>
+        <v>1889.371817</v>
       </c>
       <c r="D28" s="3">
-        <v>1495.3389999999999</v>
+        <v>1445.298</v>
       </c>
       <c r="E28" s="3">
-        <v>684.78</v>
+        <v>651.06899999999996</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>1099.656657</v>
+        <v>1101.092668</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1190,16 +1190,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1589.335703177072</v>
+        <v>1692.4931898361094</v>
       </c>
       <c r="C29" s="3">
-        <v>2117.9293490335485</v>
+        <v>2049.6583753851646</v>
       </c>
       <c r="D29" s="3">
-        <v>1917.9648966896248</v>
+        <v>1833.6980306345731</v>
       </c>
       <c r="E29" s="3">
-        <v>1093.5125527660521</v>
+        <v>1039.34265172152</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1209,22 +1209,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>2006.3286698923807</v>
+        <v>2009.7592489785143</v>
       </c>
       <c r="C30" s="5">
-        <v>2148.5269601996338</v>
+        <v>2135.879318361865</v>
       </c>
       <c r="D30" s="5">
-        <v>1741.9358968263582</v>
+        <v>1732.4344465001845</v>
       </c>
       <c r="E30" s="5">
-        <v>722.58465735914899</v>
+        <v>695.13800801688694</v>
       </c>
       <c r="F30" s="5">
-        <v>606.72076874855509</v>
+        <v>630.76201391977293</v>
       </c>
       <c r="G30" s="5">
-        <v>860.95327887854432</v>
+        <v>883.93015424832743</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
@@ -1232,20 +1232,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>2088.1111654158326</v>
+        <v>2078.6519499002875</v>
       </c>
       <c r="C31" s="5">
-        <v>2203.5830641242205</v>
+        <v>2186.9910303469769</v>
       </c>
       <c r="D31" s="5">
-        <v>1727.9934756068376</v>
+        <v>1717.7113462621253</v>
       </c>
       <c r="E31" s="5">
-        <v>741.60698823204086</v>
+        <v>718.38649809232993</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>885.65018391400179</v>
+        <v>910.30013941301911</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual/eu_wob_prices.xlsx
+++ b/data/manual/eu_wob_prices.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CE384E2-2203-4D1C-A093-5CBF013FD204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{11D18CB1-CB16-4257-A181-6304B3A3DE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
@@ -670,7 +670,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -696,13 +696,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>1865</v>
+        <v>1817</v>
       </c>
       <c r="C3" s="3">
-        <v>2162</v>
+        <v>2132</v>
       </c>
       <c r="D3" s="3">
-        <v>1820.57</v>
+        <v>1808.38</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -713,16 +713,16 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1977.27</v>
+        <v>1988.68</v>
       </c>
       <c r="C4" s="3">
-        <v>2335.08</v>
+        <v>2350.54</v>
       </c>
       <c r="D4" s="3">
-        <v>1597</v>
+        <v>1545</v>
       </c>
       <c r="E4" s="3">
-        <v>598.84</v>
+        <v>606.04999999999995</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
@@ -734,16 +734,16 @@
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1649.1</v>
+        <v>1646.3</v>
       </c>
       <c r="C5" s="3">
-        <v>1873.8</v>
+        <v>1883.7</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>598</v>
+        <v>610.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -751,20 +751,20 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1803.33</v>
+        <v>1806.5</v>
       </c>
       <c r="C6" s="3">
-        <v>1953.75</v>
+        <v>1954.13</v>
       </c>
       <c r="D6" s="3">
         <v>1620</v>
       </c>
       <c r="E6" s="3">
-        <v>940.8</v>
+        <v>975.8</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>907</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -772,13 +772,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1759.61</v>
+        <v>1759.59</v>
       </c>
       <c r="C7" s="3">
-        <v>2020.75</v>
+        <v>2017.9</v>
       </c>
       <c r="D7" s="3">
-        <v>1678.38</v>
+        <v>1682.24</v>
       </c>
       <c r="E7" s="3">
         <v>1059.51</v>
@@ -791,18 +791,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1859.0873682915831</v>
+        <v>1862.1780388612742</v>
       </c>
       <c r="C8" s="3">
-        <v>1921.2004427862737</v>
+        <v>1953.3746867682701</v>
       </c>
       <c r="D8" s="3">
-        <v>1534.8284203189701</v>
+        <v>1530.583740705747</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>927.39125087122306</v>
+        <v>955.75730189376827</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -810,13 +810,13 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2658.2651040830524</v>
+        <v>2604.7868141865229</v>
       </c>
       <c r="C9" s="3">
-        <v>2501.7391769679457</v>
+        <v>2501.7726463938352</v>
       </c>
       <c r="D9" s="3">
-        <v>2462.8083694547008</v>
+        <v>2462.8413180462094</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -827,13 +827,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>1920</v>
+        <v>1954</v>
       </c>
       <c r="C10" s="3">
-        <v>2013</v>
+        <v>2062</v>
       </c>
       <c r="D10" s="3">
-        <v>1706</v>
+        <v>1736</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -846,13 +846,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>2318.8260869565224</v>
+        <v>2327.3636363636365</v>
       </c>
       <c r="C11" s="3">
-        <v>2536.0454545454545</v>
+        <v>2531.8000000000006</v>
       </c>
       <c r="D11" s="3">
-        <v>2072.4888888888891</v>
+        <v>2084.5450000000001</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -863,18 +863,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>2212.2199999999998</v>
+        <v>2228.88</v>
       </c>
       <c r="C12" s="3">
-        <v>2328.25</v>
+        <v>2345.84</v>
       </c>
       <c r="D12" s="3">
-        <v>1892.57</v>
+        <v>1930.78</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>1028.8599999999999</v>
+        <v>1034.8800000000001</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -882,18 +882,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>2214</v>
+        <v>2179</v>
       </c>
       <c r="C13" s="3">
-        <v>2270</v>
+        <v>2266</v>
       </c>
       <c r="D13" s="3">
-        <v>1698.1</v>
+        <v>1712.8</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>1133</v>
+        <v>1095.25</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -901,12 +901,14 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>2199</v>
+        <v>2191</v>
       </c>
       <c r="C14" s="3">
-        <v>2118</v>
-      </c>
-      <c r="D14" s="3"/>
+        <v>2126</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1563</v>
+      </c>
       <c r="E14" s="3">
         <v>667.8</v>
       </c>
@@ -918,20 +920,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1754.0858764191948</v>
+        <v>1770.7850977263709</v>
       </c>
       <c r="C15" s="3">
-        <v>1941.8789433776333</v>
+        <v>1951.1841779427671</v>
       </c>
       <c r="D15" s="3">
-        <v>1941.8789433776333</v>
+        <v>1951.1841779427671</v>
       </c>
       <c r="E15" s="3">
-        <v>1304.603839728316</v>
+        <v>1444.6890478811229</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>1014.847193641408</v>
+        <v>1021.675226876398</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -939,13 +941,13 @@
         <v>24</v>
       </c>
       <c r="B16" s="3">
-        <v>1982.7</v>
+        <v>1970.8</v>
       </c>
       <c r="C16" s="3">
-        <v>2163.6999999999998</v>
+        <v>2136.6999999999998</v>
       </c>
       <c r="D16" s="3">
-        <v>1487.25</v>
+        <v>1575.95</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -956,20 +958,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>2021.02</v>
+        <v>2015.74</v>
       </c>
       <c r="C17" s="3">
-        <v>2240.73</v>
+        <v>2244.44</v>
       </c>
       <c r="D17" s="3">
-        <v>2053</v>
+        <v>2071</v>
       </c>
       <c r="E17" s="3">
-        <v>747.09</v>
+        <v>763.64</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>781.09</v>
+        <v>786.08</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -977,18 +979,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1942.8</v>
+        <v>1948.6</v>
       </c>
       <c r="C18" s="3">
-        <v>2072.17</v>
+        <v>2062.67</v>
       </c>
       <c r="D18" s="3">
-        <v>1836.21</v>
+        <v>1826.71</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>985.6</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -996,18 +998,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1924.94</v>
+        <v>1951.03</v>
       </c>
       <c r="C19" s="3">
-        <v>2205.09</v>
+        <v>2219.11</v>
       </c>
       <c r="D19" s="3">
-        <v>1577.25</v>
+        <v>1570.37</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>856.18</v>
+        <v>898.65</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1015,18 +1017,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1876</v>
+        <v>1788</v>
       </c>
       <c r="C20" s="3">
-        <v>2045</v>
+        <v>2081</v>
       </c>
       <c r="D20" s="3">
-        <v>1536</v>
+        <v>1575</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>919</v>
+        <v>953</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1051,16 +1053,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>2461.96</v>
+        <v>2390.7399999999998</v>
       </c>
       <c r="C22" s="3">
-        <v>2481.86</v>
+        <v>2456.2600000000002</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>960.92</v>
+        <v>983.98</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1068,22 +1070,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1570.2289837417384</v>
+        <v>1560.0519867116232</v>
       </c>
       <c r="C23" s="3">
-        <v>1794.6871203469439</v>
+        <v>1790.4562826637443</v>
       </c>
       <c r="D23" s="3">
-        <v>1691.4694954589233</v>
+        <v>1706.159202334868</v>
       </c>
       <c r="E23" s="3">
-        <v>753.42972262350975</v>
+        <v>840.75536406299398</v>
       </c>
       <c r="F23" s="3">
-        <v>655.41248342928134</v>
+        <v>684.43481771994311</v>
       </c>
       <c r="G23" s="3">
-        <v>773.37468583966722</v>
+        <v>806.14964713024006</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1091,20 +1093,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>2110</v>
+        <v>2099</v>
       </c>
       <c r="C24" s="3">
-        <v>2148</v>
+        <v>2175</v>
       </c>
       <c r="D24" s="3">
-        <v>2183</v>
+        <v>2222</v>
       </c>
       <c r="E24" s="3">
-        <v>1101.1300000000001</v>
+        <v>1123.68</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>934</v>
+        <v>952</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1112,20 +1114,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>1897.6203859846357</v>
+        <v>1895.3439471312709</v>
       </c>
       <c r="C25" s="3">
-        <v>2041.3022297170698</v>
+        <v>2044.3507810153201</v>
       </c>
       <c r="D25" s="3">
-        <v>1580.4684279557803</v>
+        <v>1517.7643436467408</v>
       </c>
       <c r="E25" s="3">
-        <v>1015.7729061270378</v>
+        <v>976.17152297987377</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>883.63687464867917</v>
+        <v>885.53431961550018</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1133,16 +1135,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>1846</v>
+        <v>1885</v>
       </c>
       <c r="C26" s="3">
-        <v>1919</v>
+        <v>1952</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1150,18 +1152,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1761.48</v>
+        <v>1750.63</v>
       </c>
       <c r="C27" s="3">
-        <v>1918.27</v>
+        <v>1893.35</v>
       </c>
       <c r="D27" s="3">
-        <v>1569.8</v>
+        <v>1555.87</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>981.72</v>
+        <v>994.13</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1169,20 +1171,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1789.5447049999998</v>
+        <v>1780.4743169999999</v>
       </c>
       <c r="C28" s="3">
-        <v>1889.371817</v>
+        <v>1889.2212500000001</v>
       </c>
       <c r="D28" s="3">
-        <v>1445.298</v>
+        <v>1521.3319999999999</v>
       </c>
       <c r="E28" s="3">
-        <v>651.06899999999996</v>
+        <v>661.21</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>1101.092668</v>
+        <v>1103.4040130000001</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1190,16 +1192,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1692.4931898361094</v>
+        <v>1639.9495677233431</v>
       </c>
       <c r="C29" s="3">
-        <v>2049.6583753851646</v>
+        <v>2040.3458213256488</v>
       </c>
       <c r="D29" s="3">
-        <v>1833.6980306345731</v>
+        <v>1873.2889048991358</v>
       </c>
       <c r="E29" s="3">
-        <v>1039.34265172152</v>
+        <v>1073.4870317002883</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1209,22 +1211,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>2009.7592489785143</v>
+        <v>1991.3323259570577</v>
       </c>
       <c r="C30" s="5">
-        <v>2135.879318361865</v>
+        <v>2138.6756134933908</v>
       </c>
       <c r="D30" s="5">
-        <v>1732.4344465001845</v>
+        <v>1739.7262240836417</v>
       </c>
       <c r="E30" s="5">
-        <v>695.13800801688694</v>
+        <v>706.61935479190174</v>
       </c>
       <c r="F30" s="5">
-        <v>630.76201391977293</v>
+        <v>658.69280023932583</v>
       </c>
       <c r="G30" s="5">
-        <v>883.93015424832743</v>
+        <v>890.1386106661646</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
@@ -1232,20 +1234,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>2078.6519499002875</v>
+        <v>2059.3300829950495</v>
       </c>
       <c r="C31" s="5">
-        <v>2186.9910303469769</v>
+        <v>2189.9018174993307</v>
       </c>
       <c r="D31" s="5">
-        <v>1717.7113462621253</v>
+        <v>1726.5999448495741</v>
       </c>
       <c r="E31" s="5">
-        <v>718.38649809232993</v>
+        <v>729.24112546663787</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>910.30013941301911</v>
+        <v>909.8248433690668</v>
       </c>
     </row>
   </sheetData>

--- a/data/manual/eu_wob_prices.xlsx
+++ b/data/manual/eu_wob_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11D18CB1-CB16-4257-A181-6304B3A3DE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBB0322D-B193-42E9-83C9-35B90084AC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
@@ -670,7 +670,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -696,13 +696,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>1817</v>
+        <v>1772</v>
       </c>
       <c r="C3" s="3">
         <v>2132</v>
       </c>
       <c r="D3" s="3">
-        <v>1808.38</v>
+        <v>1830.07</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -713,20 +713,20 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1988.68</v>
+        <v>1952.96</v>
       </c>
       <c r="C4" s="3">
-        <v>2350.54</v>
+        <v>2375.0500000000002</v>
       </c>
       <c r="D4" s="3">
-        <v>1545</v>
+        <v>1541.2</v>
       </c>
       <c r="E4" s="3">
-        <v>606.04999999999995</v>
+        <v>626.07000000000005</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>1079</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -734,16 +734,16 @@
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1646.3</v>
+        <v>1625</v>
       </c>
       <c r="C5" s="3">
-        <v>1883.7</v>
+        <v>1890.2</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
-        <v>610.5</v>
+        <v>622.20000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -751,20 +751,20 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1806.5</v>
+        <v>1790.83</v>
       </c>
       <c r="C6" s="3">
-        <v>1954.13</v>
+        <v>2004.63</v>
       </c>
       <c r="D6" s="3">
-        <v>1620</v>
+        <v>1660</v>
       </c>
       <c r="E6" s="3">
         <v>975.8</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>977</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -772,13 +772,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1759.59</v>
+        <v>1729.51</v>
       </c>
       <c r="C7" s="3">
-        <v>2017.9</v>
+        <v>2004.95</v>
       </c>
       <c r="D7" s="3">
-        <v>1682.24</v>
+        <v>1586.35</v>
       </c>
       <c r="E7" s="3">
         <v>1059.51</v>
@@ -791,18 +791,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1862.1780388612742</v>
+        <v>1798.2682916820552</v>
       </c>
       <c r="C8" s="3">
-        <v>1953.3746867682701</v>
+        <v>1949.5260371783825</v>
       </c>
       <c r="D8" s="3">
-        <v>1530.583740705747</v>
+        <v>1559.9942549961017</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>955.75730189376827</v>
+        <v>955.3120768189093</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -810,7 +810,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>2604.7868141865229</v>
+        <v>2524.5160340883249</v>
       </c>
       <c r="C9" s="3">
         <v>2501.7726463938352</v>
@@ -827,13 +827,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>1954</v>
+        <v>1887</v>
       </c>
       <c r="C10" s="3">
-        <v>2062</v>
+        <v>2101</v>
       </c>
       <c r="D10" s="3">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -846,13 +846,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>2327.3636363636365</v>
+        <v>2345.9090909090914</v>
       </c>
       <c r="C11" s="3">
-        <v>2531.8000000000006</v>
+        <v>2547.478260869565</v>
       </c>
       <c r="D11" s="3">
-        <v>2084.5450000000001</v>
+        <v>2092.3080555555553</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -863,18 +863,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>2228.88</v>
+        <v>2180.6799999999998</v>
       </c>
       <c r="C12" s="3">
-        <v>2345.84</v>
+        <v>2351.5300000000002</v>
       </c>
       <c r="D12" s="3">
-        <v>1930.78</v>
+        <v>1951.75</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>1034.8800000000001</v>
+        <v>1040.8399999999999</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -882,18 +882,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>2179</v>
+        <v>2167</v>
       </c>
       <c r="C13" s="3">
-        <v>2266</v>
+        <v>2298</v>
       </c>
       <c r="D13" s="3">
-        <v>1712.8</v>
+        <v>1750.1</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>1095.25</v>
+        <v>1130.25</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -901,13 +901,13 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>2191</v>
+        <v>2143</v>
       </c>
       <c r="C14" s="3">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="D14" s="3">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="E14" s="3">
         <v>667.8</v>
@@ -920,20 +920,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1770.7850977263709</v>
+        <v>1754.0209068787594</v>
       </c>
       <c r="C15" s="3">
-        <v>1951.1841779427671</v>
+        <v>1929.5678110905703</v>
       </c>
       <c r="D15" s="3">
-        <v>1951.1841779427671</v>
+        <v>1929.5678110905703</v>
       </c>
       <c r="E15" s="3">
-        <v>1444.6890478811229</v>
+        <v>1485.9164512178527</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>1021.675226876398</v>
+        <v>1022.3872608091866</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -958,20 +958,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>2015.74</v>
+        <v>2005.83</v>
       </c>
       <c r="C17" s="3">
-        <v>2244.44</v>
+        <v>2246.71</v>
       </c>
       <c r="D17" s="3">
-        <v>2071</v>
+        <v>2074.71</v>
       </c>
       <c r="E17" s="3">
-        <v>763.64</v>
+        <v>777.27</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>786.08</v>
+        <v>788.97</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -979,18 +979,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1948.6</v>
+        <v>1932.4</v>
       </c>
       <c r="C18" s="3">
-        <v>2062.67</v>
+        <v>2083.5</v>
       </c>
       <c r="D18" s="3">
-        <v>1826.71</v>
+        <v>1847.55</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>1033</v>
+        <v>1052.5</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -998,18 +998,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1951.03</v>
+        <v>1926.88</v>
       </c>
       <c r="C19" s="3">
-        <v>2219.11</v>
+        <v>2222.42</v>
       </c>
       <c r="D19" s="3">
-        <v>1570.37</v>
+        <v>1603.17</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>898.65</v>
+        <v>925.12</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1017,18 +1017,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1788</v>
+        <v>1746</v>
       </c>
       <c r="C20" s="3">
-        <v>2081</v>
+        <v>2054</v>
       </c>
       <c r="D20" s="3">
-        <v>1575</v>
+        <v>1544</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>953</v>
+        <v>943</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1053,16 +1053,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>2390.7399999999998</v>
+        <v>2312.5100000000002</v>
       </c>
       <c r="C22" s="3">
-        <v>2456.2600000000002</v>
+        <v>2469.0300000000002</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>983.98</v>
+        <v>997.13</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1070,22 +1070,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1560.0519867116232</v>
+        <v>1467.1329306508014</v>
       </c>
       <c r="C23" s="3">
-        <v>1790.4562826637443</v>
+        <v>1781.1867023933873</v>
       </c>
       <c r="D23" s="3">
-        <v>1706.159202334868</v>
+        <v>1734.1000953721784</v>
       </c>
       <c r="E23" s="3">
-        <v>840.75536406299398</v>
+        <v>867.43267178345968</v>
       </c>
       <c r="F23" s="3">
-        <v>684.43481771994311</v>
+        <v>686.03024660520452</v>
       </c>
       <c r="G23" s="3">
-        <v>806.14964713024006</v>
+        <v>812.96380398746533</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1093,20 +1093,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>2099</v>
+        <v>2040</v>
       </c>
       <c r="C24" s="3">
-        <v>2175</v>
+        <v>2189</v>
       </c>
       <c r="D24" s="3">
-        <v>2222</v>
+        <v>2242</v>
       </c>
       <c r="E24" s="3">
-        <v>1123.68</v>
+        <v>1152.22</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>952</v>
+        <v>959</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1114,20 +1114,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>1895.3439471312709</v>
+        <v>1886.4810278084267</v>
       </c>
       <c r="C25" s="3">
-        <v>2044.3507810153201</v>
+        <v>2036.508144297122</v>
       </c>
       <c r="D25" s="3">
-        <v>1517.7643436467408</v>
+        <v>1592.5289398387972</v>
       </c>
       <c r="E25" s="3">
-        <v>976.17152297987377</v>
+        <v>954.55089484412713</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>885.53431961550018</v>
+        <v>881.87496493557489</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1135,16 +1135,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>1885</v>
+        <v>1820</v>
       </c>
       <c r="C26" s="3">
-        <v>1952</v>
+        <v>1970</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1152,18 +1152,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1750.63</v>
+        <v>1731.96</v>
       </c>
       <c r="C27" s="3">
-        <v>1893.35</v>
+        <v>1909.2</v>
       </c>
       <c r="D27" s="3">
-        <v>1555.87</v>
+        <v>1573.88</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>994.13</v>
+        <v>1012.43</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1171,20 +1171,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1780.4743169999999</v>
+        <v>1751.1076729999997</v>
       </c>
       <c r="C28" s="3">
-        <v>1889.2212500000001</v>
+        <v>1887.7989109999999</v>
       </c>
       <c r="D28" s="3">
-        <v>1521.3319999999999</v>
+        <v>1507.9530000000002</v>
       </c>
       <c r="E28" s="3">
-        <v>661.21</v>
+        <v>749.6</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>1103.4040130000001</v>
+        <v>1105.009002</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1192,16 +1192,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1639.9495677233431</v>
+        <v>1560.3537280603314</v>
       </c>
       <c r="C29" s="3">
-        <v>2040.3458213256488</v>
+        <v>2037.2581586389549</v>
       </c>
       <c r="D29" s="3">
-        <v>1873.2889048991358</v>
+        <v>1869.1026619383222</v>
       </c>
       <c r="E29" s="3">
-        <v>1073.4870317002883</v>
+        <v>1060.645508820757</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1211,22 +1211,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>1991.3323259570577</v>
+        <v>1954.0378712134029</v>
       </c>
       <c r="C30" s="5">
-        <v>2138.6756134933908</v>
+        <v>2146.1859738900539</v>
       </c>
       <c r="D30" s="5">
-        <v>1739.7262240836417</v>
+        <v>1760.0420474870859</v>
       </c>
       <c r="E30" s="5">
-        <v>706.61935479190174</v>
+        <v>770.18321538920566</v>
       </c>
       <c r="F30" s="5">
-        <v>658.69280023932583</v>
+        <v>660.22822405589375</v>
       </c>
       <c r="G30" s="5">
-        <v>890.1386106661646</v>
+        <v>900.68712491834378</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
@@ -1234,20 +1234,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>2059.3300829950495</v>
+        <v>2032.0243203886089</v>
       </c>
       <c r="C31" s="5">
-        <v>2189.9018174993307</v>
+        <v>2201.2344529627385</v>
       </c>
       <c r="D31" s="5">
-        <v>1726.5999448495741</v>
+        <v>1747.2922942050611</v>
       </c>
       <c r="E31" s="5">
-        <v>729.24112546663787</v>
+        <v>798.68584250104061</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>909.8248433690668</v>
+        <v>921.70617209226691</v>
       </c>
     </row>
   </sheetData>
